--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/19,10,26 Останкино КИ и ЗПФ/машины Останкино КИ и ЗПФ.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/19,10,26 Останкино КИ и ЗПФ/машины Останкино КИ и ЗПФ.xlsx
@@ -5,16 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\10,26\19,10,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3648AB6-36CE-491D-A894-E2B1C6782061}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5D897AF-7C34-4AA9-918F-99AD71A749FC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$H$20</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -956,6 +959,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H20" xr:uid="{DB9A1683-848B-4BCC-B46D-3D590CC09480}"/>
   <mergeCells count="1">
     <mergeCell ref="C19:F19"/>
   </mergeCells>
